--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-semantic-annotations.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-semantic-annotations.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Ontology Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Type Group</t>
+    <t xml:space="preserve">Type Groups</t>
   </si>
   <si>
     <t xml:space="preserve">Meta Data</t>
@@ -155,6 +155,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
